--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650777</v>
+        <v>121650779</v>
       </c>
       <c r="B2" t="n">
-        <v>56269</v>
+        <v>56265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650780</v>
+        <v>121650782</v>
       </c>
       <c r="B3" t="n">
-        <v>56264</v>
+        <v>56251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -926,7 +926,7 @@
         <v>121650775</v>
       </c>
       <c r="B4" t="n">
-        <v>56271</v>
+        <v>56272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121650781</v>
+        <v>121650777</v>
       </c>
       <c r="B5" t="n">
-        <v>56250</v>
+        <v>56270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,30 +1059,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650780</v>
+        <v>121650775</v>
       </c>
       <c r="B2" t="n">
-        <v>56265</v>
+        <v>56272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650781</v>
+        <v>121650780</v>
       </c>
       <c r="B3" t="n">
-        <v>56251</v>
+        <v>56265</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650775</v>
+        <v>121650781</v>
       </c>
       <c r="B4" t="n">
-        <v>56272</v>
+        <v>56251</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,26 +939,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650775</v>
+        <v>121650780</v>
       </c>
       <c r="B2" t="n">
-        <v>56272</v>
+        <v>56265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650780</v>
+        <v>121650777</v>
       </c>
       <c r="B3" t="n">
-        <v>56265</v>
+        <v>56270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,26 +815,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121650777</v>
+        <v>121650775</v>
       </c>
       <c r="B5" t="n">
-        <v>56270</v>
+        <v>56272</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,30 +1059,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650780</v>
+        <v>121650775</v>
       </c>
       <c r="B2" t="n">
-        <v>56265</v>
+        <v>56272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650777</v>
+        <v>121650781</v>
       </c>
       <c r="B3" t="n">
-        <v>56270</v>
+        <v>56251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650781</v>
+        <v>121650779</v>
       </c>
       <c r="B4" t="n">
-        <v>56251</v>
+        <v>56265</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121650775</v>
+        <v>121650777</v>
       </c>
       <c r="B5" t="n">
-        <v>56272</v>
+        <v>56270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,30 +1059,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650775</v>
+        <v>121650781</v>
       </c>
       <c r="B2" t="n">
-        <v>56272</v>
+        <v>56251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650781</v>
+        <v>121650780</v>
       </c>
       <c r="B3" t="n">
-        <v>56251</v>
+        <v>56265</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650779</v>
+        <v>121650777</v>
       </c>
       <c r="B4" t="n">
-        <v>56265</v>
+        <v>56270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,26 +939,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121650777</v>
+        <v>121650775</v>
       </c>
       <c r="B5" t="n">
-        <v>56270</v>
+        <v>56272</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,30 +1059,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650781</v>
+        <v>121650782</v>
       </c>
       <c r="B2" t="n">
         <v>56251</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650777</v>
+        <v>121650775</v>
       </c>
       <c r="B4" t="n">
-        <v>56270</v>
+        <v>56272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121650775</v>
+        <v>121650777</v>
       </c>
       <c r="B5" t="n">
-        <v>56272</v>
+        <v>56270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,30 +1059,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650782</v>
+        <v>121650781</v>
       </c>
       <c r="B2" t="n">
         <v>56251</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650780</v>
+        <v>121650779</v>
       </c>
       <c r="B3" t="n">
         <v>56265</v>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650775</v>
+        <v>121650777</v>
       </c>
       <c r="B4" t="n">
-        <v>56272</v>
+        <v>56270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121650777</v>
+        <v>121650775</v>
       </c>
       <c r="B5" t="n">
-        <v>56270</v>
+        <v>56272</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,30 +1059,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650781</v>
+        <v>121650782</v>
       </c>
       <c r="B2" t="n">
-        <v>56251</v>
+        <v>56259</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,7 +802,7 @@
         <v>121650779</v>
       </c>
       <c r="B3" t="n">
-        <v>56265</v>
+        <v>56273</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>121650777</v>
       </c>
       <c r="B4" t="n">
-        <v>56270</v>
+        <v>56278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>121650775</v>
       </c>
       <c r="B5" t="n">
-        <v>56272</v>
+        <v>56280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650782</v>
+        <v>121650781</v>
       </c>
       <c r="B2" t="n">
         <v>56259</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650779</v>
+        <v>121650777</v>
       </c>
       <c r="B3" t="n">
-        <v>56273</v>
+        <v>56278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,26 +815,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650777</v>
+        <v>121650780</v>
       </c>
       <c r="B4" t="n">
-        <v>56278</v>
+        <v>56273</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,26 +939,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650781</v>
+        <v>121650775</v>
       </c>
       <c r="B2" t="n">
-        <v>56259</v>
+        <v>56280</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650777</v>
+        <v>121650781</v>
       </c>
       <c r="B3" t="n">
-        <v>56278</v>
+        <v>56259</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -923,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650780</v>
+        <v>121650779</v>
       </c>
       <c r="B4" t="n">
         <v>56273</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121650775</v>
+        <v>121650777</v>
       </c>
       <c r="B5" t="n">
-        <v>56280</v>
+        <v>56278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,30 +1059,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121650775</v>
+        <v>121650779</v>
       </c>
       <c r="B2" t="n">
-        <v>56280</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -799,42 +794,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121650781</v>
+        <v>121650777</v>
       </c>
       <c r="B3" t="n">
-        <v>56259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -923,42 +913,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121650779</v>
+        <v>121650781</v>
       </c>
       <c r="B4" t="n">
-        <v>56273</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1047,42 +1032,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121650777</v>
+        <v>121650775</v>
       </c>
       <c r="B5" t="n">
-        <v>56278</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 64789-2023 artfynd.xlsx
+++ b/artfynd/A 64789-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121650779</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121650777</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121650781</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,8 +1168,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121650775</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>